--- a/assets/templates/mau_import_tai_khoan.xlsx
+++ b/assets/templates/mau_import_tai_khoan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20373"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49F20D0-4611-4E58-86FE-09BEFE51E862}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BC7D7F8-AA8F-411C-9E89-609C64D258E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Mật khẩu</t>
-  </si>
-  <si>
     <t>Họ và tên</t>
   </si>
   <si>
@@ -52,9 +46,6 @@
     <t>nguyenvana@gmail.com</t>
   </si>
   <si>
-    <t>nguyenvana</t>
-  </si>
-  <si>
     <t>Nguyễn Văn A</t>
   </si>
   <si>
@@ -64,13 +55,16 @@
     <t>nguyenvanb@gmail.com</t>
   </si>
   <si>
-    <t>nguyenvanb</t>
-  </si>
-  <si>
     <t>Nguyễn Văn B</t>
   </si>
   <si>
     <t>CNTT2</t>
+  </si>
+  <si>
+    <t>Mã</t>
+  </si>
+  <si>
+    <t>sdfgdfsdf</t>
   </si>
 </sst>
 </file>
@@ -476,98 +470,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.88671875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="20.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" style="8" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" s="7" customFormat="1" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6">
+        <v>37761</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>20180002</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6">
+        <v>37761</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="7" customFormat="1" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="5">
-        <v>123456</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>37761</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="5">
-        <v>123456</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6">
-        <v>37761</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>8</v>
+    <row r="6" spans="1:6" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="7">
+        <v>20230001</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatRows="0" deleteRows="0"/>
   <dataValidations count="1">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vai trò" error="Vai trò chỉ được chọn student hoặc lecturer" sqref="G1:G1048576" xr:uid="{DF8233D6-F524-4BA8-A28A-F4F3B8C2294E}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vai trò" error="Vai trò chỉ được chọn student hoặc lecturer" sqref="F1:F1048576" xr:uid="{DF8233D6-F524-4BA8-A28A-F4F3B8C2294E}">
       <formula1>"student, lecturer"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{9D14C703-4C00-495C-AE86-D44B622E2020}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{9D14C703-4C00-495C-AE86-D44B622E2020}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
